--- a/Projeto/Base de dados.xlsx
+++ b/Projeto/Base de dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dudu\Documents\CLIENTES WEB\sistema_advogados\Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AA641D-CA36-432C-98B2-58998A27A260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5399A62-12EA-4E91-A099-E1D5B432E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="3390" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="142">
   <si>
     <t>Nome</t>
   </si>
@@ -157,12 +157,6 @@
   </si>
   <si>
     <t>desempregada</t>
-  </si>
-  <si>
-    <t>56.419.492/0001-09</t>
-  </si>
-  <si>
-    <t>WORKS CONSTRUCAO &amp; SERVICOS LTDA</t>
   </si>
   <si>
     <t>Lucas de Paula Alves Ferreira</t>
@@ -624,7 +618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -688,6 +682,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,623 +1058,570 @@
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="24">
         <v>47474838885</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="25">
         <v>106</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="27" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="9">
-        <v>10</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="9" t="s">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="11" t="s">
-        <v>43</v>
+      <c r="E3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="4">
+        <v>57</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="7">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="D4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="9">
         <v>49</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4">
-        <v>57</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>57</v>
+      <c r="M4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="9" t="s">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="9">
-        <v>49</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>69</v>
+      <c r="J5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="A6" s="7">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>82</v>
+      <c r="J6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="9">
+        <v>915</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="9" t="s">
+      <c r="E7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="9">
-        <v>915</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q7" s="11" t="s">
+      <c r="J7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="L7" s="4">
+        <v>623</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="A8" s="7">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="4">
-        <v>623</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="6"/>
+      <c r="J8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="L8" s="9">
+        <v>1665</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q8" s="11"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="4">
         <v>106</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="9">
-        <v>1665</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q9" s="11"/>
+      <c r="M9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="4">
-        <v>106</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="4" t="s">
+      <c r="A10" s="7">
+        <v>10</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="C10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>120</v>
       </c>
+      <c r="F10" s="12">
+        <v>16902086</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="L10" s="9">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="11"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="12">
-        <v>16902086</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="L11" s="9">
-        <v>5</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N11" s="9" t="s">
+      <c r="E11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="4">
+        <v>187</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="O11" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="A12" s="13">
+        <v>12</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="L12" s="4">
-        <v>187</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="4" t="s">
+      <c r="K12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="15">
+        <v>10</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="Q12" s="17" t="s">
         <v>141</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="15">
-        <v>10</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="23" spans="6:6" x14ac:dyDescent="0.25">
@@ -1674,15 +1630,14 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" xr:uid="{56F6B94C-C38A-437A-B71D-3AD34A5FA066}"/>
-    <hyperlink ref="O3" r:id="rId2" xr:uid="{F8CBF028-1B02-4C4F-90D2-E9B0621D2F1C}"/>
-    <hyperlink ref="O4" r:id="rId3" xr:uid="{322BB318-999E-42EE-B3A1-1EBD5BD06FC7}"/>
-    <hyperlink ref="O5" r:id="rId4" xr:uid="{ED5929DA-7832-47FA-9479-6164D27F4913}"/>
-    <hyperlink ref="O6" r:id="rId5" xr:uid="{E0282C26-1DC5-4026-9EC1-794DDF8EDE2D}"/>
-    <hyperlink ref="O7" r:id="rId6" xr:uid="{BF88E582-F43A-449F-885F-1FC67F5D4F52}"/>
-    <hyperlink ref="O8" r:id="rId7" xr:uid="{85D905F4-E535-47B4-9307-4093DF29F4E3}"/>
-    <hyperlink ref="O9" r:id="rId8" xr:uid="{E5071FA2-A4B2-4292-AE69-0A91560BAB7D}"/>
-    <hyperlink ref="O11" r:id="rId9" xr:uid="{B635FEE7-0C6B-4584-94D1-BA0CC535ACDB}"/>
-    <hyperlink ref="O12" r:id="rId10" xr:uid="{0956823D-DC13-4169-A8B4-C6CF34142818}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{322BB318-999E-42EE-B3A1-1EBD5BD06FC7}"/>
+    <hyperlink ref="O4" r:id="rId3" xr:uid="{ED5929DA-7832-47FA-9479-6164D27F4913}"/>
+    <hyperlink ref="O5" r:id="rId4" xr:uid="{E0282C26-1DC5-4026-9EC1-794DDF8EDE2D}"/>
+    <hyperlink ref="O6" r:id="rId5" xr:uid="{BF88E582-F43A-449F-885F-1FC67F5D4F52}"/>
+    <hyperlink ref="O7" r:id="rId6" xr:uid="{85D905F4-E535-47B4-9307-4093DF29F4E3}"/>
+    <hyperlink ref="O8" r:id="rId7" xr:uid="{E5071FA2-A4B2-4292-AE69-0A91560BAB7D}"/>
+    <hyperlink ref="O10" r:id="rId8" xr:uid="{B635FEE7-0C6B-4584-94D1-BA0CC535ACDB}"/>
+    <hyperlink ref="O11" r:id="rId9" xr:uid="{0956823D-DC13-4169-A8B4-C6CF34142818}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
